--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117929216</v>
+        <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>101228</v>
+        <v>100955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,16 +1915,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>222584</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1935,17 +1935,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
+          <t>Z830 Fors, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585787</v>
+        <v>585868</v>
       </c>
       <c r="R14" t="n">
-        <v>6980277</v>
+        <v>6980123</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,16 +1989,122 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136545970</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>117929216</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvarnbacken, Kvarnbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>585787</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6980277</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/117929216</t>
         </is>
@@ -2019,6 +2125,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100955</v>
+        <v>100958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100958</v>
+        <v>100959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100959</v>
+        <v>100964</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100964</v>
+        <v>100966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100966</v>
+        <v>100972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100972</v>
+        <v>100974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100974</v>
+        <v>100975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100975</v>
+        <v>100981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100981</v>
+        <v>100985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100985</v>
+        <v>100987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>100989</v>
+        <v>101002</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 14814-2024 artfynd.xlsx
+++ b/artfynd/A 14814-2024 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>136545970</v>
       </c>
       <c r="B14" t="n">
-        <v>101002</v>
+        <v>101004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
